--- a/韌體組/0719IR_Transmitter/tx_event_log.xlsx
+++ b/韌體組/0719IR_Transmitter/tx_event_log.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2224,6 +2224,4826 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>13:39:09.486</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>13:39:17.598</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>13:40:52.503</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>13:45:43.695</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>13:47:21.948</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>13:51:14.480</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>13:51:54.828</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>13:52:25.610</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>13:52:43.933</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>13:52:51.973</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>13:52:56.272</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 2</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>13:53:19.095</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 3</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>13:53:23.154</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>13:53:28.283</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM ERROR</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>13:53:39.202</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>13:53:42.511</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>13:53:58.274</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>13:55:29.527</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>13:55:44.510</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 2</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>13:55:53.679</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 3</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>13:55:56.924</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>13:56:02.298</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>13:56:18.207</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>13:57:47.083</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>23:11:50.053</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>23:13:18.334</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>23:13:23.733</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>23:13:31.276</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>23:13:39.394</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>23:13:44.584</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>23:13:48.926</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>23:13:54.529</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>23:13:58.474</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>23:14:02.963</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>23:14:08.716</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>01:22:48.201</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>01:23:04.863</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>01:23:28.078</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>01:23:34.722</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>01:23:44.415</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>01:24:08.228</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>01:24:27.098</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>01:24:31.947</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM ERROR</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>01:24:52.152</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>01:24:58.110</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>01:25:03.344</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>01:26:39.628</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>01:27:21.386</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>01:27:33.761</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>01:27:41.039</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>01:27:57.809</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>01:28:19.681</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>01:44:13.651</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>01:54:54.655</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>01:55:39.162</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>01:55:48.545</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>01:55:54.215</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>01:56:02.807</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>01:56:38.715</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>01:56:44.064</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>01:57:25.625</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>01:57:31.973</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>01:57:48.919</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>01:57:54.604</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>01:58:00.732</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>01:59:01.494</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>01:59:05.652</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>01:59:21.914</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>01:59:28.686</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>01:59:36.420</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>02:00:09.668</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>02:00:35.151</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>02:00:38.770</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>02:00:44.919</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>02:02:06.270</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>02:02:12.958</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>02:02:22.734</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>02:02:29.047</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>02:02:39.373</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>02:02:48.612</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>02:03:38.187</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>02:03:44.071</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>02:03:50.249</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>02:04:03.255</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>02:04:58.625</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>02:05:00.205</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>02:05:44.420</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>02:06:01.423</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>02:06:12.376</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>02:06:18.174</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>02:06:23.053</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>02:06:27.822</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>02:14:08.200</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>02:15:25.744</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>02:15:29.903</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>02:15:36.180</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>02:15:40.964</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>02:15:46.453</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>02:16:00.126</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>02:16:06.020</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>02:18:16.808</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>02:19:49.227</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>02:19:58.092</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>02:20:04.211</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>02:20:09.011</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>02:20:13.722</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>02:22:00.495</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>19:36:42.014</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>19:36:48.858</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>19:36:59.522</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>19:38:33.032</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>19:38:34.412</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>19:38:35.862</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>19:38:37.502</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>19:38:42.607</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>19:39:17.728</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>19:39:33.737</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>19:39:37.521</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>19:40:20.311</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>19:40:22.971</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>19:40:26.410</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>19:41:00.967</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>19:41:14.395</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>19:41:20.599</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>19:41:28.724</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>19:41:31.909</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>19:41:37.155</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>19:41:41.988</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>19:41:45.458</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>19:42:35.526</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>20:29:35.952</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>20:29:39.797</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>20:29:47.296</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>20:29:58.052</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>20:30:06.208</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>20:35:26.461</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>20:35:37.411</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>20:35:40.206</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>20:35:44.181</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>20:35:51.222</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>20:50:32.792</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>20:50:42.760</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>20:50:54.371</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>20:51:10.979</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>20:51:22.906</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>20:51:48.271</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>20:52:36.840</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>20:52:39.584</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>20:52:52.433</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>20:53:21.141</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>20:53:50.215</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>20:53:55.220</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>20:54:01.405</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>20:54:06.130</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>20:54:51.452</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>21:08:28.208</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>21:08:54.164</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>21:09:06.529</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>21:09:15.972</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>21:09:52.405</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>21:10:50.540</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>21:10:55.820</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>21:11:30.309</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>21:12:42.911</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>21:12:57.901</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>21:13:14.844</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>21:13:34.742</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>21:14:03.130</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>21:14:08.229</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>21:15:09.683</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>20:08:29.024</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>20:08:42.293</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>20:08:45.931</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>20:08:47.490</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>20:08:53.274</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>20:08:56.874</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>20:08:59.104</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>20:09:01.639</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>20:09:03.827</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>20:09:05.093</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>20:09:06.608</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>20:18:00.762</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>20:18:10.164</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>20:18:12.234</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>20:18:14.634</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>20:18:16.569</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM ERROR</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>20:18:19.888</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>20:18:21.907</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>20:18:22.843</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>20:18:25.826</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>20:18:31.061</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>20:24:24.297</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>20:24:26.171</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>20:24:28.536</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>20:24:29.711</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>20:24:31.016</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>20:27:55.047</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>20:27:55.907</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>20:27:57.622</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>20:27:59.377</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>20:28:01.186</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>20:28:03.577</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="inlineStr">
+        <is>
+          <t>20:28:05.209</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>19:37:14.374</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>19:48:16.135</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>19:48:19.520</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>19:48:21.560</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>20:29:22.360</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="inlineStr">
+        <is>
+          <t>20:29:26.814</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>20:29:52.901</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="inlineStr">
+        <is>
+          <t>20:29:54.640</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>20:29:56.076</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>20:30:00.744</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="inlineStr">
+        <is>
+          <t>20:30:02.515</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>20:30:03.589</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>20:30:04.749</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>21:16:39.174</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
+        <is>
+          <t>21:16:41.334</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>21:16:42.495</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>21:16:45.104</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>21:16:47.065</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM ERROR</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>21:16:49.045</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>21:16:50.964</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>21:00:03.578</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>21:00:19.635</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>21:00:53.376</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>21:01:33.056</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>21:01:43.874</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>21:01:58.274</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>21:02:18.361</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>21:03:22.190</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>21:03:52.396</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>21:04:38.036</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>21:04:42.554</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr">
+        <is>
+          <t>21:04:44.773</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>BRAKE Level 1</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
+          <t>21:04:46.583</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>21:04:53.828</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM ERROR</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="inlineStr">
+        <is>
+          <t>21:04:58.073</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 1</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>21:04:59.998</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 2</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="inlineStr">
+        <is>
+          <t>21:05:02.731</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>VRU Level 3</t>
+        </is>
+      </c>
+      <c r="D330" s="3" t="inlineStr">
+        <is>
+          <t>21:05:05.977</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
